--- a/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>VRDN</t>
   </si>
@@ -656,99 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2500</v>
-      </c>
-      <c r="L8" s="3">
-        <v>4300</v>
       </c>
       <c r="M8" s="3">
         <v>4300</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>4300</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -770,21 +776,24 @@
       <c r="I9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="3">
-        <v>2500</v>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K9" s="3">
         <v>2500</v>
       </c>
       <c r="L9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M9" s="3">
         <v>3200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2800</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -806,21 +815,24 @@
       <c r="I10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1500</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,44 +847,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>159300</v>
+      </c>
+      <c r="E12" s="3">
         <v>100600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>56800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,62 +922,68 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>70200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
         <v>300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>300</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>5</v>
@@ -978,9 +1000,12 @@
       <c r="M15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1017,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>254800</v>
+      </c>
+      <c r="E17" s="3">
         <v>136100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>82700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>111400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>46400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4500</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-254500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-134300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-79700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-110400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-42000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-33100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-26500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1080,152 +1112,165 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-235400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-129100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-79300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-110000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-40800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-31500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6700</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>400</v>
       </c>
       <c r="J22" s="3">
         <v>400</v>
       </c>
       <c r="K22" s="3">
+        <v>400</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2000</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-237700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-129900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-79400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-110700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-41900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-26500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2200</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1259,9 +1304,12 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1295,81 +1343,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-237700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-129900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-79400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-110700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-41900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2200</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-237700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-129900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-79400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-110700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-41900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-32700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2400</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1403,9 +1460,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1439,9 +1499,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1538,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1577,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-237700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-129900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-79400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-110700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-41900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-32700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2400</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1694,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-237700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-129900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-79400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-110700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-41900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-32700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2400</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +1797,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,64 +1814,68 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>102800</v>
+      </c>
+      <c r="E41" s="3">
         <v>155600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>45900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>24800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>47400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>374500</v>
+      </c>
+      <c r="E42" s="3">
         <v>269000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>154700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>81700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29900</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>5</v>
@@ -1800,9 +1889,12 @@
       <c r="M42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1810,143 +1902,155 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <v>1500</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
       </c>
       <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
         <v>100</v>
-      </c>
-      <c r="K44" s="3">
-        <v>200</v>
       </c>
       <c r="L44" s="3">
         <v>200</v>
       </c>
       <c r="M44" s="3">
+        <v>200</v>
+      </c>
+      <c r="N44" s="3">
         <v>400</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>486500</v>
+      </c>
+      <c r="E46" s="3">
         <v>431200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>200200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>129600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>65400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2100</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1980,45 +2084,51 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>600</v>
       </c>
       <c r="J48" s="3">
         <v>600</v>
       </c>
       <c r="K48" s="3">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="L48" s="3">
         <v>1200</v>
       </c>
       <c r="M48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N48" s="3">
         <v>900</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2052,9 +2162,12 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2201,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,45 +2240,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>900</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
       </c>
       <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>700</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2318,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>490400</v>
+      </c>
+      <c r="E54" s="3">
         <v>435100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>203700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>131300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>52500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3700</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2377,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,44 +2394,48 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E57" s="3">
         <v>14200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2312,177 +2445,192 @@
       <c r="E58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>4000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>3000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>26900</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E59" s="3">
         <v>19100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E60" s="3">
         <v>33300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27300</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4600</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>4300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
       <c r="K62" s="3">
         <v>0</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +2664,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,9 +2703,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +2742,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E66" s="3">
         <v>40000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27600</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +2801,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +2837,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,24 +2876,27 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>206500</v>
+      </c>
+      <c r="E70" s="3">
         <v>142100</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>133800</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>180800</v>
       </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
       <c r="H70" s="3">
         <v>0</v>
       </c>
@@ -2737,20 +2904,23 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>77000</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,45 +2954,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-725900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-488200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-358300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-278900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-168200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-126300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-93600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-67100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-18000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-23900</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3032,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3071,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3110,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>235500</v>
+      </c>
+      <c r="E76" s="3">
         <v>253000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>53900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-60800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>38500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-61900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-23900</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3188,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-237700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-129900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-79400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-110700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-41900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-32700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2400</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,22 +3291,23 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>500</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>300</v>
@@ -3121,17 +3319,20 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
+        <v>300</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3366,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +3405,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +3444,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +3483,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +3522,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-184200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-93800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-54600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-29800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-36100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-26800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,44 +3581,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +3656,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +3695,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-94300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-115100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-74300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-50500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>28200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,8 +3754,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3555,11 +3788,14 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-300</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +3829,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +3868,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,45 +3907,51 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>225700</v>
+      </c>
+      <c r="E100" s="3">
         <v>322200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>125300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>101300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>41900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>52500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>15900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7400</v>
       </c>
-      <c r="M100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3734,46 +3982,52 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="E102" s="3">
         <v>113300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>VRDN</t>
   </si>
@@ -758,26 +758,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>159800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100900</v>
+      </c>
+      <c r="F9" s="3">
+        <v>56900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>28300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>32800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>30400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>19600</v>
       </c>
       <c r="K9" s="3">
         <v>2500</v>
@@ -797,26 +797,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>-159500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-99100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-15600</v>
       </c>
       <c r="K10" s="3">
         <v>900</v>
@@ -854,19 +854,19 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>159300</v>
+        <v>159800</v>
       </c>
       <c r="E12" s="3">
-        <v>100600</v>
+        <v>100900</v>
       </c>
       <c r="F12" s="3">
-        <v>56800</v>
+        <v>56900</v>
       </c>
       <c r="G12" s="3">
-        <v>27800</v>
+        <v>28300</v>
       </c>
       <c r="H12" s="3">
-        <v>32800</v>
+        <v>34800</v>
       </c>
       <c r="I12" s="3">
         <v>30400</v>
@@ -937,11 +937,11 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
-        <v>70200</v>
+        <v>69900</v>
       </c>
       <c r="H14" s="3">
         <v>2000</v>
@@ -949,8 +949,8 @@
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
+      <c r="J14" s="3">
+        <v>100</v>
       </c>
       <c r="K14" s="3">
         <v>2900</v>
@@ -985,11 +985,11 @@
       <c r="H15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
+      <c r="I15" s="3">
+        <v>300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>300</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
@@ -1033,10 +1033,10 @@
         <v>82700</v>
       </c>
       <c r="G17" s="3">
-        <v>111400</v>
+        <v>41600</v>
       </c>
       <c r="H17" s="3">
-        <v>46400</v>
+        <v>44400</v>
       </c>
       <c r="I17" s="3">
         <v>41500</v>
@@ -1072,10 +1072,10 @@
         <v>-79700</v>
       </c>
       <c r="G18" s="3">
-        <v>-110400</v>
+        <v>-40500</v>
       </c>
       <c r="H18" s="3">
-        <v>-42000</v>
+        <v>-40000</v>
       </c>
       <c r="I18" s="3">
         <v>-33100</v>
@@ -1118,26 +1118,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>18600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>4900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>400</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1158,25 +1158,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-235400</v>
+        <v>-253900</v>
       </c>
       <c r="E21" s="3">
-        <v>-129100</v>
+        <v>-134000</v>
       </c>
       <c r="F21" s="3">
-        <v>-79300</v>
+        <v>-79600</v>
       </c>
       <c r="G21" s="3">
-        <v>-110000</v>
+        <v>-40300</v>
       </c>
       <c r="H21" s="3">
-        <v>-40800</v>
+        <v>-39700</v>
       </c>
       <c r="I21" s="3">
-        <v>-31500</v>
+        <v>-32800</v>
       </c>
       <c r="J21" s="3">
-        <v>-25800</v>
+        <v>-26200</v>
       </c>
       <c r="K21" s="3">
         <v>-16500</v>
@@ -1215,7 +1215,7 @@
         <v>900</v>
       </c>
       <c r="J22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K22" s="3">
         <v>400</v>
@@ -1274,26 +1274,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1586,26 +1586,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-18600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-400</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -1877,8 +1877,8 @@
       <c r="I42" s="3">
         <v>29900</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>5</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>5</v>
@@ -1911,13 +1911,13 @@
         <v>5</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J43" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1937,26 +1937,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>100</v>
@@ -1976,26 +1976,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>9000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>6500</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F45" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>3000</v>
+        <v>100</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>1900</v>
@@ -2054,26 +2054,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2261,8 +2261,8 @@
       <c r="G52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -2439,17 +2439,17 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>5</v>
+      <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>600</v>
+      </c>
+      <c r="F58" s="3">
+        <v>500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H58" s="3">
         <v>4000</v>
@@ -2479,25 +2479,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>24400</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>19100</v>
+        <v>400</v>
       </c>
       <c r="F59" s="3">
-        <v>11300</v>
+        <v>400</v>
       </c>
       <c r="G59" s="3">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="H59" s="3">
-        <v>5100</v>
+        <v>1700</v>
       </c>
       <c r="I59" s="3">
-        <v>3900</v>
+        <v>200</v>
       </c>
       <c r="J59" s="3">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="K59" s="3">
         <v>3900</v>
@@ -2557,7 +2557,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>20200</v>
+        <v>21200</v>
       </c>
       <c r="E61" s="3">
         <v>4600</v>
@@ -2595,20 +2595,20 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1600</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="F62" s="3">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
@@ -3123,7 +3123,7 @@
         <v>235500</v>
       </c>
       <c r="E76" s="3">
-        <v>253000</v>
+        <v>252900</v>
       </c>
       <c r="F76" s="3">
         <v>53900</v>
@@ -3955,26 +3955,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>VRDN</t>
   </si>
@@ -656,66 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -723,116 +726,125 @@
         <v>300</v>
       </c>
       <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>1800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2500</v>
-      </c>
-      <c r="M8" s="3">
-        <v>4300</v>
       </c>
       <c r="N8" s="3">
         <v>4300</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>4300</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>238300</v>
+      </c>
+      <c r="E9" s="3">
         <v>159800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>100900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>56900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>28300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>32800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19600</v>
-      </c>
-      <c r="K9" s="3">
-        <v>2500</v>
       </c>
       <c r="L9" s="3">
         <v>2500</v>
       </c>
       <c r="M9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N9" s="3">
         <v>3200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2800</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-238000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-159500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-99100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-53900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-27300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-28300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-22000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-15600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1500</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -848,47 +860,51 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>238300</v>
+      </c>
+      <c r="E12" s="3">
         <v>159800</v>
       </c>
-      <c r="E12" s="3">
-        <v>100900</v>
-      </c>
       <c r="F12" s="3">
+        <v>78500</v>
+      </c>
+      <c r="G12" s="3">
         <v>56900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>28300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>34800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,9 +941,12 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -940,33 +959,36 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>69900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -974,16 +996,16 @@
         <v>500</v>
       </c>
       <c r="E15" s="3">
+        <v>500</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -991,8 +1013,8 @@
       <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
+      <c r="K15" s="3">
+        <v>300</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
@@ -1003,9 +1025,12 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>299300</v>
+      </c>
+      <c r="E17" s="3">
         <v>254800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>136100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>82700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>44400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4500</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-299000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-254500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-134300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-79700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-40500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-40000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-33100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-26500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,8 +1145,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1139,138 +1172,150 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-298500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-253900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-134000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-79600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-40300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-39700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-32800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-16500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6700</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2000</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-269900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-237700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-129900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-79400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-110700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-41900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1295,8 +1340,8 @@
       <c r="J24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1307,9 +1352,12 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-269900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-237700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-129900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-79400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-110700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-41900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-32700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2200</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-237700</v>
+        <v>-208600</v>
       </c>
       <c r="E27" s="3">
-        <v>-129900</v>
+        <v>-175000</v>
       </c>
       <c r="F27" s="3">
+        <v>-87000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-79400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-110700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-41900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-32700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2400</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,9 +1646,12 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1607,60 +1676,66 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-269900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-237700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-129900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-79400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-110700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-41900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-32700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2400</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-269900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-237700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-129900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-79400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-110700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-41900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-32700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2400</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,73 +1900,77 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E41" s="3">
         <v>102800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>155600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>42300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>45900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>24800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>47400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>618000</v>
+      </c>
+      <c r="E42" s="3">
         <v>374500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>269000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>154700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>81700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>29900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>5</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>5</v>
@@ -1892,48 +1981,54 @@
       <c r="N42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>100</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
       </c>
       <c r="F43" s="3">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2600</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2000</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1958,21 +2053,24 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>100</v>
-      </c>
-      <c r="L44" s="3">
-        <v>200</v>
       </c>
       <c r="M44" s="3">
         <v>200</v>
       </c>
       <c r="N44" s="3">
+        <v>200</v>
+      </c>
+      <c r="O44" s="3">
         <v>400</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1982,12 +2080,12 @@
       <c r="E45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>5</v>
       </c>
@@ -1997,60 +2095,66 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>1900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>738500</v>
+      </c>
+      <c r="E46" s="3">
         <v>486500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>431200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>129600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>65400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>51900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2100</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2075,8 +2179,8 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2087,48 +2191,54 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>600</v>
       </c>
       <c r="K48" s="3">
         <v>600</v>
       </c>
       <c r="L48" s="3">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="M48" s="3">
         <v>1200</v>
       </c>
       <c r="N48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O48" s="3">
         <v>900</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2165,9 +2275,12 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>500</v>
+      </c>
+      <c r="E52" s="3">
         <v>600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
       <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>700</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>742400</v>
+      </c>
+      <c r="E54" s="3">
         <v>490400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>435100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>203700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>131300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>66100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>52500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3700</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,86 +2524,93 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>600</v>
-      </c>
-      <c r="F58" s="3">
-        <v>500</v>
       </c>
       <c r="G58" s="3">
         <v>500</v>
       </c>
       <c r="H58" s="3">
+        <v>500</v>
+      </c>
+      <c r="I58" s="3">
         <v>4000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2300</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>3000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>26900</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2488,149 +2624,161 @@
         <v>400</v>
       </c>
       <c r="G59" s="3">
+        <v>400</v>
+      </c>
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E60" s="3">
         <v>26600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27300</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E61" s="3">
         <v>21200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4600</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>4300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E62" s="3">
-        <v>1200</v>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F62" s="3">
         <v>1200</v>
       </c>
       <c r="G62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E66" s="3">
         <v>48400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>40000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27600</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,27 +3043,30 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>188900</v>
+      </c>
+      <c r="E70" s="3">
         <v>206500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>142100</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>133800</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>180800</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -2907,20 +3074,23 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>77000</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-995900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-725900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-488200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-358300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-278900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-168200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-126300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-93600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-67100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-18000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-23900</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>482800</v>
+      </c>
+      <c r="E76" s="3">
         <v>235500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>252900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>53900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-60800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>51300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>38500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-61900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-23900</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-269900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-237700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-129900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-79400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-110700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-41900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-32700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2400</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,8 +3489,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3301,16 +3499,16 @@
         <v>500</v>
       </c>
       <c r="E83" s="3">
+        <v>500</v>
+      </c>
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>300</v>
@@ -3322,17 +3520,20 @@
         <v>300</v>
       </c>
       <c r="L83" s="3">
+        <v>300</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-232300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-184200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-93800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-54600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-29800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-36100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-228700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-94300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-115100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-74300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-50500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>28200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,8 +3987,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3791,11 +4024,14 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-300</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,48 +4152,54 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>457700</v>
+      </c>
+      <c r="E100" s="3">
         <v>225700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>322200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>125300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>101300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>41900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>52500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>15900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7400</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3976,8 +4224,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3985,49 +4233,55 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-52800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>113300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>21100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
@@ -3496,13 +3496,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>500</v>
+        <v>1300</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>

--- a/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRDN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>VRDN</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>300</v>
+        <v>70800</v>
       </c>
       <c r="E8" s="3">
         <v>300</v>
       </c>
       <c r="F8" s="3">
+        <v>300</v>
+      </c>
+      <c r="G8" s="3">
         <v>1800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2500</v>
-      </c>
-      <c r="N8" s="3">
-        <v>4300</v>
       </c>
       <c r="O8" s="3">
         <v>4300</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>338900</v>
+      </c>
+      <c r="E9" s="3">
         <v>238300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>159800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>100900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>56900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>32800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19600</v>
-      </c>
-      <c r="L9" s="3">
-        <v>2500</v>
       </c>
       <c r="M9" s="3">
         <v>2500</v>
       </c>
       <c r="N9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O9" s="3">
         <v>3200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2800</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-268100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-238000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-159500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-99100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-53900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-27300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-28300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-22000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-15600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1500</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>338900</v>
+      </c>
+      <c r="E12" s="3">
         <v>238300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>159800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>78500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>56900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>28300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>30400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -962,33 +981,36 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>69900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-300</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -999,16 +1021,16 @@
         <v>500</v>
       </c>
       <c r="F15" s="3">
+        <v>500</v>
+      </c>
+      <c r="G15" s="3">
         <v>300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1016,8 +1038,8 @@
       <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
+      <c r="L15" s="3">
+        <v>300</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>434200</v>
+      </c>
+      <c r="E17" s="3">
         <v>299300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>254800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>136100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>82700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>44400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-363400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-299000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-254500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-134300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-79700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-40500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-40000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-33100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-26500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,19 +1178,20 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>200</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>5</v>
@@ -1175,147 +1208,159 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-298500</v>
+        <v>-364600</v>
       </c>
       <c r="E21" s="3">
-        <v>-253900</v>
+        <v>-298800</v>
       </c>
       <c r="F21" s="3">
+        <v>-254100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-134000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-79600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-40300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-39700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-32800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3000</v>
+        <v>4900</v>
       </c>
       <c r="E22" s="3">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="F22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-342600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-269900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-237700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-129900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-79400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-110700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-41900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2200</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1343,8 +1388,8 @@
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1355,9 +1400,12 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-342600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-269900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-237700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-129900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-79400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-110700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-41900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-32700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-281900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-208600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-175000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-87000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-79400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-110700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-32700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2400</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,20 +1715,23 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-200</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
@@ -1679,63 +1748,69 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-342600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-269900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-237700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-129900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-79400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-110700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-32700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-342600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-269900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-237700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-129900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-79400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-110700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-32700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,79 +1986,83 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>212400</v>
+      </c>
+      <c r="E41" s="3">
         <v>99600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>102800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>155600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>45900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>47400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>662300</v>
+      </c>
+      <c r="E42" s="3">
         <v>618000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>374500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>269000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>154700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>81700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>29900</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>5</v>
@@ -1984,51 +2073,57 @@
       <c r="O42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="3">
-        <v>100</v>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
       </c>
       <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2600</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2056,21 +2151,24 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3">
         <v>100</v>
-      </c>
-      <c r="M44" s="3">
-        <v>200</v>
       </c>
       <c r="N44" s="3">
         <v>200</v>
       </c>
       <c r="O44" s="3">
+        <v>200</v>
+      </c>
+      <c r="P44" s="3">
         <v>400</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2083,12 +2181,12 @@
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2098,63 +2196,69 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>894200</v>
+      </c>
+      <c r="E46" s="3">
         <v>738500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>486500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>431200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>200200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>129600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>65400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2100</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2182,8 +2286,8 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2194,51 +2298,57 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>600</v>
       </c>
       <c r="L48" s="3">
         <v>600</v>
       </c>
       <c r="M48" s="3">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="N48" s="3">
         <v>1200</v>
       </c>
       <c r="O48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P48" s="3">
         <v>900</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2278,9 +2388,12 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
       </c>
       <c r="L52" s="3">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>899400</v>
+      </c>
+      <c r="E54" s="3">
         <v>742400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>490400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>435100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>203700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>131300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>66100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>52500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3700</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,92 +2654,99 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
       </c>
       <c r="I58" s="3">
+        <v>500</v>
+      </c>
+      <c r="J58" s="3">
         <v>4000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>3000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>26900</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2618,7 +2754,7 @@
         <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>400</v>
@@ -2627,158 +2763,170 @@
         <v>400</v>
       </c>
       <c r="H59" s="3">
+        <v>400</v>
+      </c>
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E60" s="3">
         <v>47900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27300</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>22600</v>
+        <v>51800</v>
       </c>
       <c r="E61" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F61" s="3">
         <v>21200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4600</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>4300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1200</v>
+      <c r="D62" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G62" s="3">
         <v>1200</v>
       </c>
       <c r="H62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>177300</v>
+      </c>
+      <c r="E66" s="3">
         <v>70800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>40000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,30 +3210,33 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E70" s="3">
         <v>188900</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>206500</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>142100</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>133800</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>180800</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -3077,20 +3244,23 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>77000</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1338500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-995900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-725900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-488200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-358300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-278900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-168200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-126300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-93600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-67100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-18000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-23900</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>590100</v>
+      </c>
+      <c r="E76" s="3">
         <v>482800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>235500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>252900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>53900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-60800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>51300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>38500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-61900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-23900</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-342600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-269900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-237700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-129900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-79400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-110700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-32700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,28 +3687,29 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
@@ -3523,17 +3721,20 @@
         <v>300</v>
       </c>
       <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-276400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-232300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-184200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-93800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-54600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-29800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-36100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,8 +4021,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3811,41 +4031,44 @@
         <v>-500</v>
       </c>
       <c r="E91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-228700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-94300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-115100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-74300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-50500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>28200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4027,11 +4260,14 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-300</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,51 +4397,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>426700</v>
+      </c>
+      <c r="E100" s="3">
         <v>457700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>225700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>322200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>125300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>101300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>41900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>52500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>15900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7400</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4227,8 +4475,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4236,52 +4484,58 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-52800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>113300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
